--- a/public/exports/29189730.xlsx
+++ b/public/exports/29189730.xlsx
@@ -81,7 +81,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492007</t>
+          <t xml:space="preserve">300592, 300593, 300594</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -90,7 +90,7 @@
         </is>
       </c>
       <c r="F2">
-        <v>257</v>
+        <v>4232</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,16 +131,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492636</t>
+          <t xml:space="preserve">300595, 300596</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F3">
-        <v>4221</v>
+        <v>3584</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -181,16 +181,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492997</t>
+          <t xml:space="preserve">301493</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F4">
-        <v>297</v>
+        <v>490</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493557</t>
+          <t xml:space="preserve">301521, 301522</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>1511</v>
+        <v>5287</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5494796</t>
+          <t xml:space="preserve">303696</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">86</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F6">
-        <v>1135</v>
+        <v>1665</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5494803</t>
+          <t xml:space="preserve">303697</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">71</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F7">
-        <v>644</v>
+        <v>1542</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5494804</t>
+          <t xml:space="preserve">303698, 303699</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>1461</v>
+        <v>1764</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">5494804</t>
+          <t xml:space="preserve">303700, 303701</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F9">
-        <v>3649</v>
+        <v>1914</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5494880</t>
+          <t xml:space="preserve">304213</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F10">
-        <v>431</v>
+        <v>555</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5498977</t>
+          <t xml:space="preserve">5492007</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="F11">
-        <v>3736</v>
+        <v>257</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">732751, 5492997</t>
+          <t xml:space="preserve">5492636</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="F12">
-        <v>264</v>
+        <v>4221</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">732757, 7977454</t>
+          <t xml:space="preserve">5492997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>3040</v>
+        <v>297</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">732760, 5493917</t>
+          <t xml:space="preserve">5493557</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F14">
-        <v>534</v>
+        <v>1511</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">732779, 3044201</t>
+          <t xml:space="preserve">5494796</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">86</t>
         </is>
       </c>
       <c r="F15">
-        <v>287</v>
+        <v>1135</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">732788, 3046501</t>
+          <t xml:space="preserve">5494803</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">71</t>
         </is>
       </c>
       <c r="F16">
-        <v>538</v>
+        <v>644</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">732803, 8606020</t>
+          <t xml:space="preserve">5494804</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="F17">
-        <v>550</v>
+        <v>1461</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">732909, 5492636</t>
+          <t xml:space="preserve">5494804</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">99</t>
+          <t xml:space="preserve">68</t>
         </is>
       </c>
       <c r="F18">
-        <v>727</v>
+        <v>3649</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">732926, 3040861</t>
+          <t xml:space="preserve">5494880</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="F19">
-        <v>323</v>
+        <v>431</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7977454, 100752456</t>
+          <t xml:space="preserve">5498977</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>4858</v>
+        <v>3736</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496880</t>
+          <t xml:space="preserve">732751, 5492997</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">93</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="F21">
-        <v>1445</v>
+        <v>264</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496880</t>
+          <t xml:space="preserve">732760, 5493917</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">96</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F22">
-        <v>3683</v>
+        <v>534</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">732873, 100054186</t>
+          <t xml:space="preserve">732779, 3044201</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1140,21 +1140,21 @@
         </is>
       </c>
       <c r="F23">
-        <v>406</v>
+        <v>287</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311007899</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-09</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3045558</t>
+          <t xml:space="preserve">732788, 3046501</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1190,21 +1190,21 @@
         </is>
       </c>
       <c r="F24">
-        <v>419</v>
+        <v>538</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311008192</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-10</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1231,30 +1231,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">300592, 300593, 300594</t>
+          <t xml:space="preserve">732803, 8606020</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F25">
-        <v>4232</v>
+        <v>550</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311011902</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-13</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1281,30 +1281,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3041562</t>
+          <t xml:space="preserve">732909, 5492636</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">99</t>
         </is>
       </c>
       <c r="F26">
-        <v>5229</v>
+        <v>727</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311013103</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-21</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">100088889</t>
+          <t xml:space="preserve">732926, 3040861</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1340,26 +1340,26 @@
         </is>
       </c>
       <c r="F27">
-        <v>1413</v>
+        <v>323</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311314190</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-15</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1381,35 +1381,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492815</t>
+          <t xml:space="preserve">7977454, 100752456</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F28">
-        <v>283</v>
+        <v>4858</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418281</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-21</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1431,35 +1431,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3046494</t>
+          <t xml:space="preserve">9496880</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">93</t>
         </is>
       </c>
       <c r="F29">
-        <v>271</v>
+        <v>1445</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505850</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1481,35 +1481,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">301493</t>
+          <t xml:space="preserve">9496880</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">96</t>
         </is>
       </c>
       <c r="F30">
-        <v>490</v>
+        <v>3683</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311630811</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-26</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040637</t>
+          <t xml:space="preserve">732873, 100054186</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1540,26 +1540,26 @@
         </is>
       </c>
       <c r="F31">
-        <v>2257</v>
+        <v>406</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654734</t>
+          <t xml:space="preserve">311007899</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2023-07-09</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040759</t>
+          <t xml:space="preserve">3045558</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="F32">
-        <v>1064</v>
+        <v>419</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654726</t>
+          <t xml:space="preserve">311008192</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2023-07-10</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1631,35 +1631,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040759</t>
+          <t xml:space="preserve">732757, 7977454</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F33">
-        <v>2980</v>
+        <v>3040</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654729</t>
+          <t xml:space="preserve">311012861</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2023-08-19</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040759</t>
+          <t xml:space="preserve">3041562</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F34">
-        <v>1083</v>
+        <v>5229</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654731</t>
+          <t xml:space="preserve">311013103</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2023-08-21</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040998</t>
+          <t xml:space="preserve">100088889</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1740,16 +1740,16 @@
         </is>
       </c>
       <c r="F35">
-        <v>530</v>
+        <v>1413</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654732</t>
+          <t xml:space="preserve">311314190</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2028-05-15</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3065419</t>
+          <t xml:space="preserve">5492815</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="F36">
-        <v>3663</v>
+        <v>283</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654748</t>
+          <t xml:space="preserve">311418281</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1831,25 +1831,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3065419</t>
+          <t xml:space="preserve">3046494</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F37">
-        <v>2880</v>
+        <v>271</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654750</t>
+          <t xml:space="preserve">311505850</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3065821</t>
+          <t xml:space="preserve">3040637</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,11 +1890,11 @@
         </is>
       </c>
       <c r="F38">
-        <v>266</v>
+        <v>2257</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654758</t>
+          <t xml:space="preserve">311654734</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">9453822</t>
+          <t xml:space="preserve">3040759</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1940,11 +1940,11 @@
         </is>
       </c>
       <c r="F39">
-        <v>1810</v>
+        <v>1064</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654737</t>
+          <t xml:space="preserve">311654726</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">9453822</t>
+          <t xml:space="preserve">3040759</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1990,11 +1990,11 @@
         </is>
       </c>
       <c r="F40">
-        <v>502</v>
+        <v>2980</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654740</t>
+          <t xml:space="preserve">311654729</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502493</t>
+          <t xml:space="preserve">3040759</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F41">
-        <v>6207</v>
+        <v>1083</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655538</t>
+          <t xml:space="preserve">311654731</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502493</t>
+          <t xml:space="preserve">3040998</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F42">
-        <v>676</v>
+        <v>530</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655538</t>
+          <t xml:space="preserve">311654732</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2131,25 +2131,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502493</t>
+          <t xml:space="preserve">3065419</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F43">
-        <v>449</v>
+        <v>3663</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655538</t>
+          <t xml:space="preserve">311654748</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">3065419</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F44">
-        <v>3137</v>
+        <v>2880</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311654750</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">3065821</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F45">
-        <v>1186</v>
+        <v>266</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311654758</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2281,25 +2281,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">9453822</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>1314</v>
+        <v>1810</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311654737</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2331,25 +2331,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">9453822</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F47">
-        <v>877</v>
+        <v>502</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311654740</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">5502493</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F48">
-        <v>532</v>
+        <v>6207</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311655538</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">5502493</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F49">
-        <v>596</v>
+        <v>676</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311655538</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">5502493</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F50">
-        <v>1014</v>
+        <v>449</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311655538</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492753</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2540,16 +2540,16 @@
         </is>
       </c>
       <c r="F51">
-        <v>1053</v>
+        <v>3137</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669156</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-24</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491443</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F52">
-        <v>652</v>
+        <v>1186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670738</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491443</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F53">
-        <v>525</v>
+        <v>1314</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670738</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,25 +2681,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F54">
-        <v>3337</v>
+        <v>877</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2740,16 +2740,16 @@
         </is>
       </c>
       <c r="F55">
-        <v>3178</v>
+        <v>532</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,16 +2790,16 @@
         </is>
       </c>
       <c r="F56">
-        <v>351</v>
+        <v>596</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="F57">
-        <v>1220</v>
+        <v>1014</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,25 +2881,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">5492753</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F58">
-        <v>298</v>
+        <v>1053</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311669156</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,25 +2931,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7148772</t>
+          <t xml:space="preserve">5491443</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F59">
-        <v>262</v>
+        <v>652</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680205</t>
+          <t xml:space="preserve">311670738</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-11</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025706</t>
+          <t xml:space="preserve">5491443</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F60">
-        <v>2242</v>
+        <v>525</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689543</t>
+          <t xml:space="preserve">311670738</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025706</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F61">
-        <v>395</v>
+        <v>3337</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689549</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,25 +3081,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025706</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F62">
-        <v>288</v>
+        <v>3178</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689543</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501290</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F63">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311692552</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-04</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">3024601</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F64">
-        <v>441</v>
+        <v>1220</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311693119</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-05</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">3024964</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F65">
-        <v>384</v>
+        <v>298</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698030</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-04</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3024964</t>
+          <t xml:space="preserve">7148772</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F66">
-        <v>1096</v>
+        <v>262</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698032</t>
+          <t xml:space="preserve">311680205</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-04</t>
+          <t xml:space="preserve">2033-05-11</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3024966</t>
+          <t xml:space="preserve">3025706</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3340,16 +3340,16 @@
         </is>
       </c>
       <c r="F67">
-        <v>1108</v>
+        <v>2242</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698057</t>
+          <t xml:space="preserve">311689543</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-04</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025373</t>
+          <t xml:space="preserve">3025706</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F68">
-        <v>2788</v>
+        <v>395</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701468</t>
+          <t xml:space="preserve">311689544</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025373</t>
+          <t xml:space="preserve">3025706</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="F69">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701468</t>
+          <t xml:space="preserve">311689543</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491965</t>
+          <t xml:space="preserve">3024964</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3490,16 +3490,16 @@
         </is>
       </c>
       <c r="F70">
-        <v>3696</v>
+        <v>384</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701474</t>
+          <t xml:space="preserve">311698030</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491965</t>
+          <t xml:space="preserve">3024964</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3540,16 +3540,16 @@
         </is>
       </c>
       <c r="F71">
-        <v>2867</v>
+        <v>1096</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701476</t>
+          <t xml:space="preserve">311698032</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493910</t>
+          <t xml:space="preserve">3024966</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="F72">
-        <v>1265</v>
+        <v>1108</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701470</t>
+          <t xml:space="preserve">311698057</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3631,20 +3631,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5500649</t>
+          <t xml:space="preserve">3025373</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F73">
-        <v>1033</v>
+        <v>2788</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701478</t>
+          <t xml:space="preserve">311701468</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9397813</t>
+          <t xml:space="preserve">3025373</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F74">
-        <v>729</v>
+        <v>310</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704954</t>
+          <t xml:space="preserve">311701468</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-05</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">9397813</t>
+          <t xml:space="preserve">5491965</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F75">
-        <v>4050</v>
+        <v>3696</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704954</t>
+          <t xml:space="preserve">311701474</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-05</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3035955</t>
+          <t xml:space="preserve">5491965</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3790,16 +3790,16 @@
         </is>
       </c>
       <c r="F76">
-        <v>297</v>
+        <v>2867</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706201</t>
+          <t xml:space="preserve">311701476</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-08</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042925</t>
+          <t xml:space="preserve">5493910</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3840,16 +3840,16 @@
         </is>
       </c>
       <c r="F77">
-        <v>6241</v>
+        <v>1265</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706453</t>
+          <t xml:space="preserve">311701470</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-11</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042925</t>
+          <t xml:space="preserve">5500649</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3890,16 +3890,16 @@
         </is>
       </c>
       <c r="F78">
-        <v>1070</v>
+        <v>1033</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706455</t>
+          <t xml:space="preserve">311701478</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-11</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5498945</t>
+          <t xml:space="preserve">9397813</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="F79">
-        <v>2517</v>
+        <v>729</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706432</t>
+          <t xml:space="preserve">311704954</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-11</t>
+          <t xml:space="preserve">2033-09-05</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3041837</t>
+          <t xml:space="preserve">9397813</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F80">
-        <v>2512</v>
+        <v>4050</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706969</t>
+          <t xml:space="preserve">311704954</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-05</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,25 +4031,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3041851</t>
+          <t xml:space="preserve">3035955</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F81">
-        <v>457</v>
+        <v>297</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706709</t>
+          <t xml:space="preserve">311706201</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-08</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492884</t>
+          <t xml:space="preserve">3042925</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="F82">
-        <v>658</v>
+        <v>6241</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706812</t>
+          <t xml:space="preserve">311706453</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,25 +4131,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493984</t>
+          <t xml:space="preserve">3042925</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F83">
-        <v>687</v>
+        <v>1070</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706970</t>
+          <t xml:space="preserve">311706455</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493984</t>
+          <t xml:space="preserve">5498945</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F84">
-        <v>501</v>
+        <v>2517</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706971</t>
+          <t xml:space="preserve">311706432</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,20 +4231,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493984</t>
+          <t xml:space="preserve">3041837</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>470</v>
+        <v>2512</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706971</t>
+          <t xml:space="preserve">311706969</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501886</t>
+          <t xml:space="preserve">3041851</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="F86">
-        <v>297</v>
+        <v>457</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706715</t>
+          <t xml:space="preserve">311706709</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8179275</t>
+          <t xml:space="preserve">5492884</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,11 +4340,11 @@
         </is>
       </c>
       <c r="F87">
-        <v>2147</v>
+        <v>658</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706669</t>
+          <t xml:space="preserve">311706812</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8523427</t>
+          <t xml:space="preserve">5493984</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4390,11 +4390,11 @@
         </is>
       </c>
       <c r="F88">
-        <v>1004</v>
+        <v>687</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706769</t>
+          <t xml:space="preserve">311706970</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">3024601</t>
+          <t xml:space="preserve">5493984</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F89">
-        <v>2393</v>
+        <v>501</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707843</t>
+          <t xml:space="preserve">311706971</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-15</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">300595, 300596</t>
+          <t xml:space="preserve">5493984</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F90">
-        <v>3584</v>
+        <v>470</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708218</t>
+          <t xml:space="preserve">311706971</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010297</t>
+          <t xml:space="preserve">5501886</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4540,16 +4540,16 @@
         </is>
       </c>
       <c r="F91">
-        <v>523</v>
+        <v>297</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708184</t>
+          <t xml:space="preserve">311706715</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,25 +4581,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010297</t>
+          <t xml:space="preserve">8179275</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F92">
-        <v>513</v>
+        <v>2147</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708184</t>
+          <t xml:space="preserve">311706669</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4631,25 +4631,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010297</t>
+          <t xml:space="preserve">8523427</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F93">
-        <v>515</v>
+        <v>1004</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708184</t>
+          <t xml:space="preserve">311706769</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4686,11 +4686,11 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F94">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4736,11 +4736,11 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F95">
-        <v>424</v>
+        <v>513</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4786,15 +4786,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F96">
-        <v>727</v>
+        <v>515</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708187</t>
+          <t xml:space="preserve">311708184</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">303696</t>
+          <t xml:space="preserve">9010297</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F97">
-        <v>1665</v>
+        <v>521</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708547</t>
+          <t xml:space="preserve">311708184</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-19</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4881,25 +4881,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">303697</t>
+          <t xml:space="preserve">9010297</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F98">
-        <v>1542</v>
+        <v>424</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708547</t>
+          <t xml:space="preserve">311708184</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-19</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4931,25 +4931,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">303698, 303699</t>
+          <t xml:space="preserve">9010297</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F99">
-        <v>1764</v>
+        <v>727</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708547</t>
+          <t xml:space="preserve">311708187</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-19</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,25 +4981,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">303700, 303701</t>
+          <t xml:space="preserve">5495445</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F100">
-        <v>1914</v>
+        <v>2074</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708549</t>
+          <t xml:space="preserve">311709756</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-19</t>
+          <t xml:space="preserve">2033-09-22</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5036,11 +5036,11 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F101">
-        <v>2074</v>
+        <v>554</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5086,11 +5086,11 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F102">
-        <v>554</v>
+        <v>1376</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5136,11 +5136,11 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F103">
-        <v>1376</v>
+        <v>1116</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5181,25 +5181,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5495445</t>
+          <t xml:space="preserve">5496355</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>1116</v>
+        <v>4264</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311709756</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-22</t>
+          <t xml:space="preserve">2033-09-26</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5236,15 +5236,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F105">
-        <v>4264</v>
+        <v>285</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710303</t>
+          <t xml:space="preserve">311710301</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5286,15 +5286,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F106">
-        <v>285</v>
+        <v>557</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710301</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5336,15 +5336,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F107">
-        <v>557</v>
+        <v>1303</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710304</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5386,15 +5386,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F108">
-        <v>1303</v>
+        <v>4350</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710306</t>
+          <t xml:space="preserve">311710293</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5436,15 +5436,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F109">
-        <v>4350</v>
+        <v>550</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710293</t>
+          <t xml:space="preserve">311710300</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5481,25 +5481,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5496355</t>
+          <t xml:space="preserve">3036596</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F110">
-        <v>550</v>
+        <v>7230</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710300</t>
+          <t xml:space="preserve">311725292</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-26</t>
+          <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">301521, 301522</t>
+          <t xml:space="preserve">3039760</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5540,16 +5540,16 @@
         </is>
       </c>
       <c r="F111">
-        <v>5287</v>
+        <v>2607</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311718541</t>
+          <t xml:space="preserve">311725294</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-30</t>
+          <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5581,20 +5581,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3036596</t>
+          <t xml:space="preserve">3039760</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F112">
-        <v>7230</v>
+        <v>512</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725292</t>
+          <t xml:space="preserve">311725294</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5636,15 +5636,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F113">
-        <v>2607</v>
+        <v>448</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725294</t>
+          <t xml:space="preserve">311725297</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5686,11 +5686,11 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F114">
-        <v>512</v>
+        <v>607</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -5731,20 +5731,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3039760</t>
+          <t xml:space="preserve">9596835</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F115">
-        <v>448</v>
+        <v>650</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725297</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5781,20 +5781,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3039760</t>
+          <t xml:space="preserve">9596835</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F116">
-        <v>607</v>
+        <v>1355</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725294</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5836,15 +5836,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F117">
-        <v>650</v>
+        <v>804</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725281</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5886,15 +5886,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F118">
-        <v>1355</v>
+        <v>1386</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725283</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5936,15 +5936,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F119">
-        <v>804</v>
+        <v>1071</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725288</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">9596835</t>
+          <t xml:space="preserve">3045483</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>1386</v>
+        <v>318</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725284</t>
+          <t xml:space="preserve">311726927</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-28</t>
+          <t xml:space="preserve">2033-12-05</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,25 +6031,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9596835</t>
+          <t xml:space="preserve">3041562</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F121">
-        <v>1071</v>
+        <v>285</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725277</t>
+          <t xml:space="preserve">311728523</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-28</t>
+          <t xml:space="preserve">2033-12-12</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3045483</t>
+          <t xml:space="preserve">3046492</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="F122">
-        <v>318</v>
+        <v>2553</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726927</t>
+          <t xml:space="preserve">311729117</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-05</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3041562</t>
+          <t xml:space="preserve">3046494</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F123">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728523</t>
+          <t xml:space="preserve">311729120</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-12</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3046492</t>
+          <t xml:space="preserve">5495136</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="F124">
-        <v>2553</v>
+        <v>550</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729117</t>
+          <t xml:space="preserve">311731468</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-01-02</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3046494</t>
+          <t xml:space="preserve">5495697</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="F125">
-        <v>341</v>
+        <v>1403</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729120</t>
+          <t xml:space="preserve">311731472</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-01-02</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5495136</t>
+          <t xml:space="preserve">7408142</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,11 +6290,11 @@
         </is>
       </c>
       <c r="F126">
-        <v>550</v>
+        <v>455</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731468</t>
+          <t xml:space="preserve">311731470</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5495697</t>
+          <t xml:space="preserve">5496106</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>1403</v>
+        <v>810</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731472</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-02</t>
+          <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6386,20 +6386,20 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F128">
-        <v>810</v>
+        <v>289</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731496</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-02</t>
+          <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6436,20 +6436,20 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F129">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731496</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-02</t>
+          <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6486,20 +6486,20 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F130">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731496</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-02</t>
+          <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6536,20 +6536,20 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F131">
-        <v>1269</v>
+        <v>269</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731496</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-02</t>
+          <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">7408142</t>
+          <t xml:space="preserve">5496106</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F132">
-        <v>455</v>
+        <v>675</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731470</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-02</t>
+          <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6636,15 +6636,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F133">
-        <v>289</v>
+        <v>351</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733225</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6686,15 +6686,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F134">
-        <v>261</v>
+        <v>1269</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733225</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6731,25 +6731,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5496106</t>
+          <t xml:space="preserve">100110802</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F135">
-        <v>675</v>
+        <v>268</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733224</t>
+          <t xml:space="preserve">311733638</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-15</t>
+          <t xml:space="preserve">2034-01-17</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5496106</t>
+          <t xml:space="preserve">5493557</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F136">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733224</t>
+          <t xml:space="preserve">311733627</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-15</t>
+          <t xml:space="preserve">2034-01-17</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,20 +6831,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">100110802</t>
+          <t xml:space="preserve">5496837</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F137">
-        <v>268</v>
+        <v>550</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733638</t>
+          <t xml:space="preserve">311733632</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493557</t>
+          <t xml:space="preserve">100047171</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F138">
-        <v>373</v>
+        <v>656</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733627</t>
+          <t xml:space="preserve">311736881</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-17</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5496837</t>
+          <t xml:space="preserve">3025373</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F139">
-        <v>550</v>
+        <v>333</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733632</t>
+          <t xml:space="preserve">311736855</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-17</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,20 +6981,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047171</t>
+          <t xml:space="preserve">3027337</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F140">
-        <v>656</v>
+        <v>439</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736881</t>
+          <t xml:space="preserve">311736852</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -7031,20 +7031,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025373</t>
+          <t xml:space="preserve">3042676</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F141">
-        <v>333</v>
+        <v>295</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736855</t>
+          <t xml:space="preserve">311736870</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3027337</t>
+          <t xml:space="preserve">3042704</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7090,11 +7090,11 @@
         </is>
       </c>
       <c r="F142">
-        <v>439</v>
+        <v>3282</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736852</t>
+          <t xml:space="preserve">311736857</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">304213</t>
+          <t xml:space="preserve">3042704</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7140,11 +7140,11 @@
         </is>
       </c>
       <c r="F143">
-        <v>555</v>
+        <v>344</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736874</t>
+          <t xml:space="preserve">311736857</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -7181,20 +7181,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042676</t>
+          <t xml:space="preserve">3042704</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F144">
-        <v>295</v>
+        <v>1578</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736870</t>
+          <t xml:space="preserve">311736857</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042704</t>
+          <t xml:space="preserve">3042866</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7240,11 +7240,11 @@
         </is>
       </c>
       <c r="F145">
-        <v>3282</v>
+        <v>487</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736857</t>
+          <t xml:space="preserve">311736872</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -7281,20 +7281,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042704</t>
+          <t xml:space="preserve">5491669</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F146">
-        <v>344</v>
+        <v>397</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736857</t>
+          <t xml:space="preserve">311736787</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -7331,20 +7331,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042704</t>
+          <t xml:space="preserve">5492636</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F147">
-        <v>1578</v>
+        <v>1491</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736857</t>
+          <t xml:space="preserve">311736908</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042866</t>
+          <t xml:space="preserve">8081921</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7390,11 +7390,11 @@
         </is>
       </c>
       <c r="F148">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736872</t>
+          <t xml:space="preserve">311736877</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7431,20 +7431,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491669</t>
+          <t xml:space="preserve">8589400</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F149">
-        <v>397</v>
+        <v>611</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736787</t>
+          <t xml:space="preserve">311736876</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7481,20 +7481,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492636</t>
+          <t xml:space="preserve">9353541</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F150">
-        <v>1491</v>
+        <v>1461</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736908</t>
+          <t xml:space="preserve">311736865</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8081921</t>
+          <t xml:space="preserve">9496868</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7540,11 +7540,11 @@
         </is>
       </c>
       <c r="F151">
-        <v>472</v>
+        <v>268</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736877</t>
+          <t xml:space="preserve">311736772</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7581,20 +7581,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589400</t>
+          <t xml:space="preserve">9530274</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F152">
-        <v>611</v>
+        <v>369</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736876</t>
+          <t xml:space="preserve">311736860</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7631,20 +7631,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9353541</t>
+          <t xml:space="preserve">9530274</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F153">
-        <v>1461</v>
+        <v>2655</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736865</t>
+          <t xml:space="preserve">311736860</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7681,20 +7681,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496868</t>
+          <t xml:space="preserve">9530274</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F154">
-        <v>268</v>
+        <v>583</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736772</t>
+          <t xml:space="preserve">311736861</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7736,15 +7736,15 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F155">
-        <v>369</v>
+        <v>1047</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736860</t>
+          <t xml:space="preserve">311736864</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530274</t>
+          <t xml:space="preserve">5491524</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="F156">
-        <v>2655</v>
+        <v>1344</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736860</t>
+          <t xml:space="preserve">311737156</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-05</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530274</t>
+          <t xml:space="preserve">5491524</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F157">
-        <v>583</v>
+        <v>436</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736861</t>
+          <t xml:space="preserve">311737156</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-05</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,25 +7881,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530274</t>
+          <t xml:space="preserve">5491524</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F158">
-        <v>1047</v>
+        <v>622</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736864</t>
+          <t xml:space="preserve">311737156</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-05</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491524</t>
+          <t xml:space="preserve">9496699</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F159">
-        <v>1344</v>
+        <v>1871</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737158</t>
+          <t xml:space="preserve">311738156</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-05</t>
+          <t xml:space="preserve">2034-02-09</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491524</t>
+          <t xml:space="preserve">732757, 7977454</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F160">
-        <v>436</v>
+        <v>4654</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737158</t>
+          <t xml:space="preserve">311739990</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-05</t>
+          <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491524</t>
+          <t xml:space="preserve">732757, 7977454</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F161">
-        <v>622</v>
+        <v>5674</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737158</t>
+          <t xml:space="preserve">311739981</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-05</t>
+          <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496699</t>
+          <t xml:space="preserve">8740862</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F162">
-        <v>1871</v>
+        <v>594</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738156</t>
+          <t xml:space="preserve">311740301</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-09</t>
+          <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">732757, 7977454</t>
+          <t xml:space="preserve">5499761</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F163">
-        <v>4654</v>
+        <v>874</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739990</t>
+          <t xml:space="preserve">311740499</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-20</t>
+          <t xml:space="preserve">2034-02-22</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">732757, 7977454</t>
+          <t xml:space="preserve">3036009</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F164">
-        <v>5674</v>
+        <v>566</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739981</t>
+          <t xml:space="preserve">311741805</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-20</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740862</t>
+          <t xml:space="preserve">7198165</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8240,16 +8240,16 @@
         </is>
       </c>
       <c r="F165">
-        <v>594</v>
+        <v>550</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740301</t>
+          <t xml:space="preserve">311741807</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-21</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5499761</t>
+          <t xml:space="preserve">8179274</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8290,16 +8290,16 @@
         </is>
       </c>
       <c r="F166">
-        <v>874</v>
+        <v>667</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740499</t>
+          <t xml:space="preserve">311741806</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-22</t>
+          <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3036009</t>
+          <t xml:space="preserve">8179299</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8340,11 +8340,11 @@
         </is>
       </c>
       <c r="F167">
-        <v>566</v>
+        <v>1409</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741805</t>
+          <t xml:space="preserve">311741810</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">7198165</t>
+          <t xml:space="preserve">5491443</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F168">
-        <v>550</v>
+        <v>366</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741807</t>
+          <t xml:space="preserve">311742630</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-04</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">8179274</t>
+          <t xml:space="preserve">732757, 7977454</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F169">
-        <v>667</v>
+        <v>5293</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741806</t>
+          <t xml:space="preserve">311742672</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-04</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8179299</t>
+          <t xml:space="preserve">9496873</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8490,16 +8490,16 @@
         </is>
       </c>
       <c r="F170">
-        <v>1409</v>
+        <v>3856</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741810</t>
+          <t xml:space="preserve">311742680</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-28</t>
+          <t xml:space="preserve">2034-03-04</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,25 +8531,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491443</t>
+          <t xml:space="preserve">8295421</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F171">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742630</t>
+          <t xml:space="preserve">311743323</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-04</t>
+          <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">732757, 7977454</t>
+          <t xml:space="preserve">8295421</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8590,16 +8590,16 @@
         </is>
       </c>
       <c r="F172">
-        <v>5293</v>
+        <v>1152</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742672</t>
+          <t xml:space="preserve">311743324</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-04</t>
+          <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496873</t>
+          <t xml:space="preserve">8295421</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="F173">
-        <v>3856</v>
+        <v>557</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742680</t>
+          <t xml:space="preserve">311743330</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-04</t>
+          <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8686,15 +8686,15 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F174">
-        <v>306</v>
+        <v>1113</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743323</t>
+          <t xml:space="preserve">311743325</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8731,20 +8731,20 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295421</t>
+          <t xml:space="preserve">8900464</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F175">
-        <v>1152</v>
+        <v>2078</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743324</t>
+          <t xml:space="preserve">311743372</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8781,20 +8781,20 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295421</t>
+          <t xml:space="preserve">8900464</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F176">
-        <v>557</v>
+        <v>1301</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743333</t>
+          <t xml:space="preserve">311743377</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8831,20 +8831,20 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295421</t>
+          <t xml:space="preserve">8900464</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F177">
-        <v>1113</v>
+        <v>2050</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743325</t>
+          <t xml:space="preserve">311743372</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8886,11 +8886,11 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F178">
-        <v>2078</v>
+        <v>1361</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -8936,15 +8936,15 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F179">
-        <v>1301</v>
+        <v>550</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743377</t>
+          <t xml:space="preserve">311743372</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -8981,20 +8981,20 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">8900464</t>
+          <t xml:space="preserve">9496913</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F180">
-        <v>2050</v>
+        <v>1181</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743372</t>
+          <t xml:space="preserve">311743174</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8900464</t>
+          <t xml:space="preserve">3036787</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F181">
-        <v>1361</v>
+        <v>361</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743372</t>
+          <t xml:space="preserve">311744546</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-06</t>
+          <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8900464</t>
+          <t xml:space="preserve">5498606</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F182">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743372</t>
+          <t xml:space="preserve">311744843</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-06</t>
+          <t xml:space="preserve">2034-03-13</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496913</t>
+          <t xml:space="preserve">5499762</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F183">
-        <v>1181</v>
+        <v>478</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743174</t>
+          <t xml:space="preserve">311746181</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-06</t>
+          <t xml:space="preserve">2034-03-19</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3036787</t>
+          <t xml:space="preserve">3036596</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F184">
-        <v>361</v>
+        <v>2720</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744546</t>
+          <t xml:space="preserve">311750522</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-12</t>
+          <t xml:space="preserve">2034-04-09</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5498606</t>
+          <t xml:space="preserve">732766, 3035967</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9240,16 +9240,16 @@
         </is>
       </c>
       <c r="F185">
-        <v>558</v>
+        <v>2168</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744843</t>
+          <t xml:space="preserve">311750512</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-13</t>
+          <t xml:space="preserve">2034-04-09</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5499762</t>
+          <t xml:space="preserve">732767, 3046461</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F186">
-        <v>478</v>
+        <v>2292</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311746181</t>
+          <t xml:space="preserve">311750509</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-19</t>
+          <t xml:space="preserve">2034-04-09</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,20 +9331,20 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">3036596</t>
+          <t xml:space="preserve">732772, 3044147</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F187">
-        <v>2720</v>
+        <v>2128</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750522</t>
+          <t xml:space="preserve">311750516</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -9381,20 +9381,20 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">732766, 3035967</t>
+          <t xml:space="preserve">9496867</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F188">
-        <v>2168</v>
+        <v>1754</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750512</t>
+          <t xml:space="preserve">311750518</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">732767, 3046461</t>
+          <t xml:space="preserve">732768, 100031195</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9440,16 +9440,16 @@
         </is>
       </c>
       <c r="F189">
-        <v>2292</v>
+        <v>2220</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750509</t>
+          <t xml:space="preserve">311752290</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-09</t>
+          <t xml:space="preserve">2034-04-16</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">732772, 3044147</t>
+          <t xml:space="preserve">5493912</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9490,16 +9490,16 @@
         </is>
       </c>
       <c r="F190">
-        <v>2128</v>
+        <v>768</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750516</t>
+          <t xml:space="preserve">311790506</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-09</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496867</t>
+          <t xml:space="preserve">7260703</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -9540,16 +9540,16 @@
         </is>
       </c>
       <c r="F191">
-        <v>1754</v>
+        <v>2058</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750518</t>
+          <t xml:space="preserve">311790502</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-09</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">732768, 100031195</t>
+          <t xml:space="preserve">7260703</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F192">
-        <v>2220</v>
+        <v>768</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311752290</t>
+          <t xml:space="preserve">311790505</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-16</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,20 +9631,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493912</t>
+          <t xml:space="preserve">7260703</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F193">
-        <v>768</v>
+        <v>2003</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790506</t>
+          <t xml:space="preserve">311790507</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -9686,20 +9686,20 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F194">
-        <v>2058</v>
+        <v>1191</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790502</t>
+          <t xml:space="preserve">311791281</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2034-10-14</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,25 +9731,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260703</t>
+          <t xml:space="preserve">3035656</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F195">
-        <v>768</v>
+        <v>341</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790505</t>
+          <t xml:space="preserve">311793836</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2034-10-28</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,25 +9781,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260703</t>
+          <t xml:space="preserve">5501290</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F196">
-        <v>2003</v>
+        <v>352</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790507</t>
+          <t xml:space="preserve">311820308</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2035-03-26</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260703</t>
+          <t xml:space="preserve">100051727</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9840,16 +9840,16 @@
         </is>
       </c>
       <c r="F197">
-        <v>1191</v>
+        <v>741</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311791281</t>
+          <t xml:space="preserve">311825790</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-14</t>
+          <t xml:space="preserve">2035-04-16</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,25 +9881,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3035656</t>
+          <t xml:space="preserve">100051727</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F198">
-        <v>341</v>
+        <v>2724</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311793836</t>
+          <t xml:space="preserve">311825793</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-28</t>
+          <t xml:space="preserve">2035-04-16</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051727</t>
+          <t xml:space="preserve">9269819</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -9940,16 +9940,16 @@
         </is>
       </c>
       <c r="F199">
-        <v>741</v>
+        <v>447</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311825790</t>
+          <t xml:space="preserve">311828739</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-16</t>
+          <t xml:space="preserve">2035-05-01</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,25 +9981,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">100051727</t>
+          <t xml:space="preserve">9269819</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F200">
-        <v>2724</v>
+        <v>1602</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311825793</t>
+          <t xml:space="preserve">311828740</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-16</t>
+          <t xml:space="preserve">2035-05-01</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9269819</t>
+          <t xml:space="preserve">7878798</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -10040,16 +10040,16 @@
         </is>
       </c>
       <c r="F201">
-        <v>447</v>
+        <v>585</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311828739</t>
+          <t xml:space="preserve">311829609</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-01</t>
+          <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,25 +10081,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">9269819</t>
+          <t xml:space="preserve">100516258</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F202">
-        <v>1602</v>
+        <v>1160</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311828740</t>
+          <t xml:space="preserve">311885461</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-01</t>
+          <t xml:space="preserve">2036-03-04</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7878798</t>
+          <t xml:space="preserve">3024601</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -10140,16 +10140,16 @@
         </is>
       </c>
       <c r="F203">
-        <v>585</v>
+        <v>2393</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311829609</t>
+          <t xml:space="preserve">311885460</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-06</t>
+          <t xml:space="preserve">2036-03-04</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10181,20 +10181,20 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">100516258</t>
+          <t xml:space="preserve">3024601</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F204">
-        <v>1160</v>
+        <v>441</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885461</t>
+          <t xml:space="preserve">311885460</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">

--- a/public/exports/29189730.xlsx
+++ b/public/exports/29189730.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 13</t>
+          <t xml:space="preserve">Bodøvej 22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,16 +101,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300592, 300593, 300594</t>
+          <t xml:space="preserve">732803, 8606020</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H2">
-        <v>4232</v>
+        <v>550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bergmannsvej 17</t>
+          <t xml:space="preserve">Brændeskovvej 2B</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,7 +161,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300595, 300596</t>
+          <t xml:space="preserve">732788, 3046501</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -170,7 +170,7 @@
         </is>
       </c>
       <c r="H3">
-        <v>3584</v>
+        <v>538</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egemosevej 3</t>
+          <t xml:space="preserve">Frederiksø 16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5882</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">301493</t>
+          <t xml:space="preserve">5492636</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="H4">
-        <v>490</v>
+        <v>4221</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syrenvej 24</t>
+          <t xml:space="preserve">Frederiksø 8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">301521, 301522</t>
+          <t xml:space="preserve">732909, 5492636</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">99</t>
         </is>
       </c>
       <c r="H5">
-        <v>5287</v>
+        <v>727</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aldersro 10</t>
+          <t xml:space="preserve">Fruerstuevej 17B</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">303696</t>
+          <t xml:space="preserve">5493557</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H6">
-        <v>1665</v>
+        <v>1511</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aldersro 8</t>
+          <t xml:space="preserve">Fruestræde 15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">303697</t>
+          <t xml:space="preserve">5492007</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>1542</v>
+        <v>257</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aldersro 6</t>
+          <t xml:space="preserve">Grønnemosevej 7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">303698, 303699</t>
+          <t xml:space="preserve">5498977</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>1764</v>
+        <v>3736</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aldersro 4</t>
+          <t xml:space="preserve">Jessens Mole 2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">303700, 303701</t>
+          <t xml:space="preserve">732751, 5492997</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="H9">
-        <v>1914</v>
+        <v>264</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grubbemøllevej 20</t>
+          <t xml:space="preserve">Jessens Mole 6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">304213</t>
+          <t xml:space="preserve">5492997</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>555</v>
+        <v>297</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fruestræde 15</t>
+          <t xml:space="preserve">Nordre Kajgade 1A</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492007</t>
+          <t xml:space="preserve">5494880</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">56</t>
         </is>
       </c>
       <c r="H11">
-        <v>257</v>
+        <v>431</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksø 16</t>
+          <t xml:space="preserve">Rolf Krakes Vej 20A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492636</t>
+          <t xml:space="preserve">732779, 3044201</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>4221</v>
+        <v>287</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jessens Mole 6</t>
+          <t xml:space="preserve">Ryttervej 70</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492997</t>
+          <t xml:space="preserve">7977454, 100752456</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H13">
-        <v>297</v>
+        <v>4858</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fruerstuevej 17B</t>
+          <t xml:space="preserve">Skolebakken 9A</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5762</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493557</t>
+          <t xml:space="preserve">732926, 3040861</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H14">
-        <v>1511</v>
+        <v>323</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kajgade 23</t>
+          <t xml:space="preserve">Troensegårdsvej 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -881,16 +881,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5494796</t>
+          <t xml:space="preserve">9496880</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">86</t>
+          <t xml:space="preserve">93</t>
         </is>
       </c>
       <c r="H15">
-        <v>1135</v>
+        <v>1445</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Havnevej 6</t>
+          <t xml:space="preserve">Østre Havnevej 20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1001,16 +1001,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5494804</t>
+          <t xml:space="preserve">732760, 5493917</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">59</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H17">
-        <v>1461</v>
+        <v>534</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Havnevej 8</t>
+          <t xml:space="preserve">Østre Havnevej 6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1066,11 +1066,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">68</t>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="H18">
-        <v>3649</v>
+        <v>1461</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Kajgade 1A</t>
+          <t xml:space="preserve">Østre Havnevej 8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5494880</t>
+          <t xml:space="preserve">5494804</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">56</t>
+          <t xml:space="preserve">68</t>
         </is>
       </c>
       <c r="H19">
-        <v>431</v>
+        <v>3649</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnemosevej 7</t>
+          <t xml:space="preserve">Østre Kajgade 11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1181,16 +1181,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5498977</t>
+          <t xml:space="preserve">9496880</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">96</t>
         </is>
       </c>
       <c r="H20">
-        <v>3736</v>
+        <v>3683</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jessens Mole 2</t>
+          <t xml:space="preserve">Østre Kajgade 23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">732751, 5492997</t>
+          <t xml:space="preserve">5494796</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">40</t>
+          <t xml:space="preserve">86</t>
         </is>
       </c>
       <c r="H21">
-        <v>264</v>
+        <v>1135</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Havnevej 20</t>
+          <t xml:space="preserve">Eskærvej 63C</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,30 +1301,30 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">732760, 5493917</t>
+          <t xml:space="preserve">732873, 100054186</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H22">
-        <v>534</v>
+        <v>406</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311007899</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-07-09</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolf Krakes Vej 20A</t>
+          <t xml:space="preserve">Bergmannsvej 64</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">732779, 3044201</t>
+          <t xml:space="preserve">3045558</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="H23">
-        <v>287</v>
+        <v>419</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311008192</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-07-10</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændeskovvej 2B</t>
+          <t xml:space="preserve">Caroline Amalie Vej 13</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">732788, 3046501</t>
+          <t xml:space="preserve">300592, 300593, 300594</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="H24">
-        <v>538</v>
+        <v>4232</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311011902</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-08-13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bodøvej 22</t>
+          <t xml:space="preserve">Ryttervej 76</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1481,30 +1481,30 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">732803, 8606020</t>
+          <t xml:space="preserve">732757, 7977454</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H25">
-        <v>550</v>
+        <v>3040</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311012861</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-08-19</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1531,40 +1531,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksø 8</t>
+          <t xml:space="preserve">Østergade 53</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5881</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">732909, 5492636</t>
+          <t xml:space="preserve">3041562</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">99</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>727</v>
+        <v>5229</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311013103</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-08-21</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 9A</t>
+          <t xml:space="preserve">Sofielund Skovvej 180</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">732926, 3040861</t>
+          <t xml:space="preserve">100088889</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1610,26 +1610,26 @@
         </is>
       </c>
       <c r="H27">
-        <v>323</v>
+        <v>1413</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311314190</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2028-05-15</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryttervej 70</t>
+          <t xml:space="preserve">Egensevej 8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,35 +1661,35 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7977454, 100752456</t>
+          <t xml:space="preserve">5492815</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H28">
-        <v>4858</v>
+        <v>283</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311418281</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troensegårdsvej 2</t>
+          <t xml:space="preserve">Skolevej 6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,35 +1721,35 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496880</t>
+          <t xml:space="preserve">3046494</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">93</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H29">
-        <v>1445</v>
+        <v>271</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311505850</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1771,45 +1771,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kajgade 11</t>
+          <t xml:space="preserve">Egemosevej 3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5882</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496880</t>
+          <t xml:space="preserve">301493</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">96</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H30">
-        <v>3683</v>
+        <v>490</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311630811</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2032-09-26</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1831,17 +1831,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 63C</t>
+          <t xml:space="preserve">Enghavevej 6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5762</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">732873, 100054186</t>
+          <t xml:space="preserve">3040998</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1850,26 +1850,26 @@
         </is>
       </c>
       <c r="H31">
-        <v>406</v>
+        <v>530</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311007899</t>
+          <t xml:space="preserve">311654732</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-09</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1891,17 +1891,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bergmannsvej 64</t>
+          <t xml:space="preserve">Fåborgvej 60</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5762</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3045558</t>
+          <t xml:space="preserve">3065419</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1910,26 +1910,26 @@
         </is>
       </c>
       <c r="H32">
-        <v>419</v>
+        <v>3663</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311008192</t>
+          <t xml:space="preserve">311654748</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-07-10</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1951,45 +1951,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryttervej 76</t>
+          <t xml:space="preserve">Fåborgvej 60</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5762</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">732757, 7977454</t>
+          <t xml:space="preserve">3065419</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H33">
-        <v>3040</v>
+        <v>2880</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311012861</t>
+          <t xml:space="preserve">311654750</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-19</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2011,17 +2011,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 53</t>
+          <t xml:space="preserve">Skolebakken 6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5881</t>
+          <t xml:space="preserve">5762</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3041562</t>
+          <t xml:space="preserve">3040637</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,26 +2030,26 @@
         </is>
       </c>
       <c r="H34">
-        <v>5229</v>
+        <v>2257</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311013103</t>
+          <t xml:space="preserve">311654734</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-08-21</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -2071,17 +2071,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofielund Skovvej 180</t>
+          <t xml:space="preserve">Svendborgvej 135</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5762</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">100088889</t>
+          <t xml:space="preserve">9453822</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="H35">
-        <v>1413</v>
+        <v>1810</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311314190</t>
+          <t xml:space="preserve">311654737</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-15</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2131,35 +2131,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egensevej 8</t>
+          <t xml:space="preserve">Svendborgvej 135</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5762</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492815</t>
+          <t xml:space="preserve">9453822</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H36">
-        <v>283</v>
+        <v>502</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418281</t>
+          <t xml:space="preserve">311654740</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-21</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2191,35 +2191,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 6</t>
+          <t xml:space="preserve">Svendborgvej 16A</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5762</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3046494</t>
+          <t xml:space="preserve">3040759</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H37">
-        <v>271</v>
+        <v>1064</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505850</t>
+          <t xml:space="preserve">311654726</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 6</t>
+          <t xml:space="preserve">Svendborgvej 16B</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,20 +2261,20 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040637</t>
+          <t xml:space="preserve">3040759</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H38">
-        <v>2257</v>
+        <v>2980</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654734</t>
+          <t xml:space="preserve">311654729</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendborgvej 16A</t>
+          <t xml:space="preserve">Svendborgvej 16C</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2326,15 +2326,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H39">
-        <v>1064</v>
+        <v>1083</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654726</t>
+          <t xml:space="preserve">311654731</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendborgvej 16B</t>
+          <t xml:space="preserve">Vestre Stationsvej 2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2381,20 +2381,20 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040759</t>
+          <t xml:space="preserve">3065821</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>2980</v>
+        <v>266</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654729</t>
+          <t xml:space="preserve">311654758</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendborgvej 16C</t>
+          <t xml:space="preserve">A P Møllers Vej 37A</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040759</t>
+          <t xml:space="preserve">5502493</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H41">
-        <v>1083</v>
+        <v>6207</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654731</t>
+          <t xml:space="preserve">311655538</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 6</t>
+          <t xml:space="preserve">A P Møllers Vej 37A</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040998</t>
+          <t xml:space="preserve">5502493</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H42">
-        <v>530</v>
+        <v>676</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654732</t>
+          <t xml:space="preserve">311655538</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2551,35 +2551,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 60</t>
+          <t xml:space="preserve">A P Møllers Vej 37A</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3065419</t>
+          <t xml:space="preserve">5502493</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H43">
-        <v>3663</v>
+        <v>449</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654748</t>
+          <t xml:space="preserve">311655538</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2611,35 +2611,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 60</t>
+          <t xml:space="preserve">Eskærvej 69</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3065419</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H44">
-        <v>2880</v>
+        <v>3137</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654753</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2671,35 +2671,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Stationsvej 2</t>
+          <t xml:space="preserve">Eskærvej 69</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3065821</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H45">
-        <v>266</v>
+        <v>1186</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654758</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2731,35 +2731,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendborgvej 135</t>
+          <t xml:space="preserve">Eskærvej 69</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">9453822</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H46">
-        <v>1810</v>
+        <v>1314</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654737</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2791,35 +2791,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svendborgvej 135</t>
+          <t xml:space="preserve">Eskærvej 69</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5762</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">9453822</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H47">
-        <v>502</v>
+        <v>877</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654740</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">A P Møllers Vej 37A</t>
+          <t xml:space="preserve">Eskærvej 69</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,25 +2861,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502493</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H48">
-        <v>6207</v>
+        <v>532</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655538</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">A P Møllers Vej 37A</t>
+          <t xml:space="preserve">Eskærvej 69</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,25 +2921,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502493</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H49">
-        <v>676</v>
+        <v>596</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655538</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">A P Møllers Vej 37A</t>
+          <t xml:space="preserve">Eskærvej 69</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502493</t>
+          <t xml:space="preserve">9462267</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H50">
-        <v>449</v>
+        <v>1014</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655538</t>
+          <t xml:space="preserve">311660442</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-23</t>
+          <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 69</t>
+          <t xml:space="preserve">Jessens Mole 11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">5492753</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3050,16 +3050,16 @@
         </is>
       </c>
       <c r="H51">
-        <v>3137</v>
+        <v>1053</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311669156</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 69</t>
+          <t xml:space="preserve">Bagergade 67A</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,25 +3101,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">5491443</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H52">
-        <v>1186</v>
+        <v>525</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311670738</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 69</t>
+          <t xml:space="preserve">Bagergade 69A</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,25 +3161,25 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">5491443</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H53">
-        <v>1314</v>
+        <v>652</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311670738</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 69</t>
+          <t xml:space="preserve">Østre Skolevej 2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,25 +3221,25 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H54">
-        <v>877</v>
+        <v>3337</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 69</t>
+          <t xml:space="preserve">Østre Skolevej 2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3290,16 +3290,16 @@
         </is>
       </c>
       <c r="H55">
-        <v>532</v>
+        <v>3178</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 69</t>
+          <t xml:space="preserve">Østre Skolevej 2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="H56">
-        <v>596</v>
+        <v>351</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 69</t>
+          <t xml:space="preserve">Østre Skolevej 2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9462267</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="H57">
-        <v>1014</v>
+        <v>1220</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311660442</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-15</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jessens Mole 11</t>
+          <t xml:space="preserve">Østre Skolevej 4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,25 +3461,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492753</t>
+          <t xml:space="preserve">8151444</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H58">
-        <v>1053</v>
+        <v>298</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669156</t>
+          <t xml:space="preserve">311673192</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-24</t>
+          <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,35 +3511,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagergade 69A</t>
+          <t xml:space="preserve">Østergade 61</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5881</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491443</t>
+          <t xml:space="preserve">7148772</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H59">
-        <v>652</v>
+        <v>262</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670738</t>
+          <t xml:space="preserve">311680205</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-05-11</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagergade 67A</t>
+          <t xml:space="preserve">Skolevej 50</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5874</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491443</t>
+          <t xml:space="preserve">3025706</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H60">
-        <v>525</v>
+        <v>2242</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670738</t>
+          <t xml:space="preserve">311689543</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,35 +3631,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Skolevej 2</t>
+          <t xml:space="preserve">Skolevej 50</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5874</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">3025706</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H61">
-        <v>3337</v>
+        <v>288</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311689543</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,35 +3691,35 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Skolevej 2</t>
+          <t xml:space="preserve">Skolevej 52</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5874</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">3025706</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H62">
-        <v>3178</v>
+        <v>395</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311689549</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,35 +3751,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Skolevej 2</t>
+          <t xml:space="preserve">Storkehavevej 2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5884</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">3024964</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311698030</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,35 +3811,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Skolevej 2</t>
+          <t xml:space="preserve">Storkehavevej 4A</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5884</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">3024964</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H64">
-        <v>1220</v>
+        <v>1096</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311698032</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Skolevej 4</t>
+          <t xml:space="preserve">Storkehavevej 8</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5884</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8151444</t>
+          <t xml:space="preserve">3024966</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H65">
-        <v>298</v>
+        <v>1108</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673192</t>
+          <t xml:space="preserve">311698057</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-13</t>
+          <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,35 +3931,35 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 61</t>
+          <t xml:space="preserve">Klostervænget 5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5881</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7148772</t>
+          <t xml:space="preserve">5500649</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H66">
-        <v>262</v>
+        <v>1033</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680205</t>
+          <t xml:space="preserve">311701478</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-11</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 50</t>
+          <t xml:space="preserve">Ramsherred 5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5874</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025706</t>
+          <t xml:space="preserve">5491965</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="H67">
-        <v>2242</v>
+        <v>3696</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689544</t>
+          <t xml:space="preserve">311701474</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 52</t>
+          <t xml:space="preserve">Ramsherred 9</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5874</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025706</t>
+          <t xml:space="preserve">5491965</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H68">
-        <v>395</v>
+        <v>2867</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689544</t>
+          <t xml:space="preserve">311701476</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 50</t>
+          <t xml:space="preserve">Storkehavevej 9</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5874</t>
+          <t xml:space="preserve">5884</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025706</t>
+          <t xml:space="preserve">3025373</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H69">
-        <v>288</v>
+        <v>2788</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689544</t>
+          <t xml:space="preserve">311701468</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-21</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storkehavevej 2</t>
+          <t xml:space="preserve">Storkehavevej 9</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3024964</t>
+          <t xml:space="preserve">3025373</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H70">
-        <v>384</v>
+        <v>310</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698030</t>
+          <t xml:space="preserve">311701468</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-04</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storkehavevej 4A</t>
+          <t xml:space="preserve">Svinget 3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5884</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3024964</t>
+          <t xml:space="preserve">5493910</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>1096</v>
+        <v>1265</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698032</t>
+          <t xml:space="preserve">311701470</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-04</t>
+          <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storkehavevej 8</t>
+          <t xml:space="preserve">Dronningemaen 30</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5884</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3024966</t>
+          <t xml:space="preserve">9397813</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="H72">
-        <v>1108</v>
+        <v>729</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698057</t>
+          <t xml:space="preserve">311704954</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-04</t>
+          <t xml:space="preserve">2033-09-05</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storkehavevej 9</t>
+          <t xml:space="preserve">Dronningemaen 30</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5884</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025373</t>
+          <t xml:space="preserve">9397813</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H73">
-        <v>2788</v>
+        <v>4050</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701468</t>
+          <t xml:space="preserve">311704954</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-09-05</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,35 +4411,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storkehavevej 9</t>
+          <t xml:space="preserve">Vindeby Pilevej 29A</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5884</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025373</t>
+          <t xml:space="preserve">3035955</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H74">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701468</t>
+          <t xml:space="preserve">311706201</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-09-08</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsherred 5</t>
+          <t xml:space="preserve">Bodøvej 18</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491965</t>
+          <t xml:space="preserve">5498945</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4490,16 +4490,16 @@
         </is>
       </c>
       <c r="H75">
-        <v>3696</v>
+        <v>2517</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701474</t>
+          <t xml:space="preserve">311706432</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,35 +4531,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramsherred 9</t>
+          <t xml:space="preserve">Hostrupvej 1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5771</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491965</t>
+          <t xml:space="preserve">3042925</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H76">
-        <v>2867</v>
+        <v>6241</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701476</t>
+          <t xml:space="preserve">311706453</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 3</t>
+          <t xml:space="preserve">Hostrupvej 1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5771</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493910</t>
+          <t xml:space="preserve">3042925</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H77">
-        <v>1265</v>
+        <v>1070</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701470</t>
+          <t xml:space="preserve">311706455</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervænget 5</t>
+          <t xml:space="preserve">Høje Bøge Vej 5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,25 +4661,25 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5500649</t>
+          <t xml:space="preserve">5501886</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H78">
-        <v>1033</v>
+        <v>297</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311701478</t>
+          <t xml:space="preserve">311706715</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-21</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningemaen 30</t>
+          <t xml:space="preserve">Kærvej 8</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5881</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9397813</t>
+          <t xml:space="preserve">3041837</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4730,16 +4730,16 @@
         </is>
       </c>
       <c r="H79">
-        <v>729</v>
+        <v>2512</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704954</t>
+          <t xml:space="preserve">311706969</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-05</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronningemaen 30</t>
+          <t xml:space="preserve">Sankt Jørgens Vej 13</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,25 +4781,25 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">9397813</t>
+          <t xml:space="preserve">5492884</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>4050</v>
+        <v>658</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704954</t>
+          <t xml:space="preserve">311706812</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-05</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeby Pilevej 29A</t>
+          <t xml:space="preserve">Skovsbovej 101</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,25 +4841,25 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">3035955</t>
+          <t xml:space="preserve">8523427</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H81">
-        <v>297</v>
+        <v>1004</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706201</t>
+          <t xml:space="preserve">311706769</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-08</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hostrupvej 1</t>
+          <t xml:space="preserve">Stenpladsen 5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5771</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042925</t>
+          <t xml:space="preserve">5493984</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="H82">
-        <v>6241</v>
+        <v>687</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706453</t>
+          <t xml:space="preserve">311706970</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-11</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,17 +4951,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hostrupvej 1</t>
+          <t xml:space="preserve">Stenpladsen 7</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5771</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042925</t>
+          <t xml:space="preserve">5493984</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4970,16 +4970,16 @@
         </is>
       </c>
       <c r="H83">
-        <v>1070</v>
+        <v>501</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706455</t>
+          <t xml:space="preserve">311706971</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-11</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bodøvej 18</t>
+          <t xml:space="preserve">Stenpladsen 9</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,25 +5021,25 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">5498945</t>
+          <t xml:space="preserve">5493984</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H84">
-        <v>2517</v>
+        <v>470</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706432</t>
+          <t xml:space="preserve">311706971</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-11</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærvej 8</t>
+          <t xml:space="preserve">Vindeby Pilevej 26</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5881</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3041837</t>
+          <t xml:space="preserve">8179275</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5090,11 +5090,11 @@
         </is>
       </c>
       <c r="H85">
-        <v>2512</v>
+        <v>2147</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706969</t>
+          <t xml:space="preserve">311706669</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sankt Jørgens Vej 13</t>
+          <t xml:space="preserve">Bergmannsvej 17</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492884</t>
+          <t xml:space="preserve">300595, 300596</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>658</v>
+        <v>3584</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706812</t>
+          <t xml:space="preserve">311708218</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenpladsen 5</t>
+          <t xml:space="preserve">Skovsbovej 111A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493984</t>
+          <t xml:space="preserve">9010297</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,16 +5270,16 @@
         </is>
       </c>
       <c r="H88">
-        <v>687</v>
+        <v>523</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706970</t>
+          <t xml:space="preserve">311708184</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenpladsen 7</t>
+          <t xml:space="preserve">Skovsbovej 111B</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493984</t>
+          <t xml:space="preserve">9010297</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5330,16 +5330,16 @@
         </is>
       </c>
       <c r="H89">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706971</t>
+          <t xml:space="preserve">311708184</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stenpladsen 9</t>
+          <t xml:space="preserve">Skovsbovej 111C</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493984</t>
+          <t xml:space="preserve">9010297</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5390,16 +5390,16 @@
         </is>
       </c>
       <c r="H90">
-        <v>470</v>
+        <v>515</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706971</t>
+          <t xml:space="preserve">311708184</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høje Bøge Vej 5</t>
+          <t xml:space="preserve">Skovsbovej 111D</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501886</t>
+          <t xml:space="preserve">9010297</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H91">
-        <v>297</v>
+        <v>521</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706715</t>
+          <t xml:space="preserve">311708184</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vindeby Pilevej 26</t>
+          <t xml:space="preserve">Skovsbovej 111E</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,25 +5501,25 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8179275</t>
+          <t xml:space="preserve">9010297</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H92">
-        <v>2147</v>
+        <v>424</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706669</t>
+          <t xml:space="preserve">311708184</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsbovej 101</t>
+          <t xml:space="preserve">Skovsbovej 111F</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5561,25 +5561,25 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8523427</t>
+          <t xml:space="preserve">9010297</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H93">
-        <v>1004</v>
+        <v>727</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706769</t>
+          <t xml:space="preserve">311708187</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsbovej 111A</t>
+          <t xml:space="preserve">Aldersro 10</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,25 +5621,25 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010297</t>
+          <t xml:space="preserve">303696</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H94">
-        <v>523</v>
+        <v>1665</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708184</t>
+          <t xml:space="preserve">311708547</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsbovej 111B</t>
+          <t xml:space="preserve">Aldersro 4</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010297</t>
+          <t xml:space="preserve">303700, 303701</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="H95">
-        <v>513</v>
+        <v>1914</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708184</t>
+          <t xml:space="preserve">311708549</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsbovej 111C</t>
+          <t xml:space="preserve">Aldersro 6</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,25 +5741,25 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010297</t>
+          <t xml:space="preserve">303698, 303699</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H96">
-        <v>515</v>
+        <v>1764</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708184</t>
+          <t xml:space="preserve">311708547</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsbovej 111D</t>
+          <t xml:space="preserve">Aldersro 8</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010297</t>
+          <t xml:space="preserve">303697</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="H97">
-        <v>521</v>
+        <v>1542</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708184</t>
+          <t xml:space="preserve">311708547</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsbovej 111E</t>
+          <t xml:space="preserve">Graaesvej 27</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,25 +5861,25 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010297</t>
+          <t xml:space="preserve">5495445</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H98">
-        <v>424</v>
+        <v>2074</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708184</t>
+          <t xml:space="preserve">311709756</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-22</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovsbovej 111F</t>
+          <t xml:space="preserve">Graaesvej 27</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5921,25 +5921,25 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9010297</t>
+          <t xml:space="preserve">5495445</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H99">
-        <v>727</v>
+        <v>554</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311708187</t>
+          <t xml:space="preserve">311709756</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-18</t>
+          <t xml:space="preserve">2033-09-22</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5986,11 +5986,11 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H100">
-        <v>2074</v>
+        <v>1376</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6046,11 +6046,11 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H101">
-        <v>554</v>
+        <v>1116</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graaesvej 27</t>
+          <t xml:space="preserve">Marslevvej 1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,25 +6101,25 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5495445</t>
+          <t xml:space="preserve">5496355</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H102">
-        <v>1376</v>
+        <v>4264</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311709756</t>
+          <t xml:space="preserve">311710303</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-22</t>
+          <t xml:space="preserve">2033-09-26</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graaesvej 27</t>
+          <t xml:space="preserve">Marslevvej 1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,25 +6161,25 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5495445</t>
+          <t xml:space="preserve">5496355</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H103">
-        <v>1116</v>
+        <v>285</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311709756</t>
+          <t xml:space="preserve">311710301</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-22</t>
+          <t xml:space="preserve">2033-09-26</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6226,15 +6226,15 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H104">
-        <v>4264</v>
+        <v>557</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710304</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6286,15 +6286,15 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H105">
-        <v>285</v>
+        <v>1303</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710306</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6346,15 +6346,15 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H106">
-        <v>557</v>
+        <v>4350</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710293</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marslevvej 1</t>
+          <t xml:space="preserve">Marslevvej 1A</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6406,15 +6406,15 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H107">
-        <v>1303</v>
+        <v>550</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710306</t>
+          <t xml:space="preserve">311710300</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marslevvej 1</t>
+          <t xml:space="preserve">Syrenvej 24</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,25 +6461,25 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5496355</t>
+          <t xml:space="preserve">301521, 301522</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H108">
-        <v>4350</v>
+        <v>5287</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311718541</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-26</t>
+          <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marslevvej 1A</t>
+          <t xml:space="preserve">Bergmannsvej 23</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,25 +6521,25 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5496355</t>
+          <t xml:space="preserve">9596835</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H109">
-        <v>550</v>
+        <v>804</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710300</t>
+          <t xml:space="preserve">311725288</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-26</t>
+          <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyrekredsen 12</t>
+          <t xml:space="preserve">Bergmannsvej 25</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3036596</t>
+          <t xml:space="preserve">9596835</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6590,11 +6590,11 @@
         </is>
       </c>
       <c r="H110">
-        <v>7230</v>
+        <v>650</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725292</t>
+          <t xml:space="preserve">311725281</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbyvej 43A</t>
+          <t xml:space="preserve">Bergmannsvej 25</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,20 +6641,20 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3039760</t>
+          <t xml:space="preserve">9596835</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H111">
-        <v>2607</v>
+        <v>1355</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725294</t>
+          <t xml:space="preserve">311725283</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbyvej 43A</t>
+          <t xml:space="preserve">Bergmannsvej 25</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,20 +6701,20 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">3039760</t>
+          <t xml:space="preserve">9596835</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H112">
-        <v>512</v>
+        <v>1386</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725294</t>
+          <t xml:space="preserve">311725284</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbyvej 43A</t>
+          <t xml:space="preserve">Bergmannsvej 25</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6761,20 +6761,20 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3039760</t>
+          <t xml:space="preserve">9596835</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H113">
-        <v>448</v>
+        <v>1071</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725297</t>
+          <t xml:space="preserve">311725277</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbyvej 43A</t>
+          <t xml:space="preserve">Dyrekredsen 12</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6821,20 +6821,20 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3039760</t>
+          <t xml:space="preserve">3036596</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H114">
-        <v>607</v>
+        <v>7230</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725294</t>
+          <t xml:space="preserve">311725292</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bergmannsvej 25</t>
+          <t xml:space="preserve">Lundbyvej 43A</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9596835</t>
+          <t xml:space="preserve">3039760</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6890,11 +6890,11 @@
         </is>
       </c>
       <c r="H115">
-        <v>650</v>
+        <v>2607</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725279</t>
+          <t xml:space="preserve">311725294</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bergmannsvej 25</t>
+          <t xml:space="preserve">Lundbyvej 43A</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6941,20 +6941,20 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">9596835</t>
+          <t xml:space="preserve">3039760</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H116">
-        <v>1355</v>
+        <v>512</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725279</t>
+          <t xml:space="preserve">311725294</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bergmannsvej 23</t>
+          <t xml:space="preserve">Lundbyvej 43A</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">9596835</t>
+          <t xml:space="preserve">3039760</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7010,11 +7010,11 @@
         </is>
       </c>
       <c r="H117">
-        <v>804</v>
+        <v>448</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725279</t>
+          <t xml:space="preserve">311725297</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bergmannsvej 25</t>
+          <t xml:space="preserve">Lundbyvej 43A</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,20 +7061,20 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">9596835</t>
+          <t xml:space="preserve">3039760</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H118">
-        <v>1386</v>
+        <v>607</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725279</t>
+          <t xml:space="preserve">311725294</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bergmannsvej 25</t>
+          <t xml:space="preserve">Gambøtvej 2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7121,25 +7121,25 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9596835</t>
+          <t xml:space="preserve">3045483</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H119">
-        <v>1071</v>
+        <v>318</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725277</t>
+          <t xml:space="preserve">311726927</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-28</t>
+          <t xml:space="preserve">2033-12-05</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,35 +7171,35 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gambøtvej 2</t>
+          <t xml:space="preserve">Nørremarken 11</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5881</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">3045483</t>
+          <t xml:space="preserve">3041562</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H120">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726927</t>
+          <t xml:space="preserve">311728523</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-05</t>
+          <t xml:space="preserve">2033-12-12</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,35 +7231,35 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarken 11</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5881</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3041562</t>
+          <t xml:space="preserve">3046492</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H121">
-        <v>285</v>
+        <v>2553</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728523</t>
+          <t xml:space="preserve">311729117</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-12</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Skolevej 6</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3046492</t>
+          <t xml:space="preserve">3046494</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7310,11 +7310,11 @@
         </is>
       </c>
       <c r="H122">
-        <v>2553</v>
+        <v>341</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729117</t>
+          <t xml:space="preserve">311729120</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 6</t>
+          <t xml:space="preserve">Skovbrynet 1A</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3046494</t>
+          <t xml:space="preserve">5495697</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7370,16 +7370,16 @@
         </is>
       </c>
       <c r="H123">
-        <v>341</v>
+        <v>1403</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729120</t>
+          <t xml:space="preserve">311731472</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-01-02</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 1A</t>
+          <t xml:space="preserve">Slotsvængevej 14</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5495697</t>
+          <t xml:space="preserve">7408142</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,11 +7490,11 @@
         </is>
       </c>
       <c r="H125">
-        <v>1403</v>
+        <v>455</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731472</t>
+          <t xml:space="preserve">311731470</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsvængevej 14</t>
+          <t xml:space="preserve">St Byhavevej 67</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,25 +7541,25 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">7408142</t>
+          <t xml:space="preserve">5496106</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H126">
-        <v>455</v>
+        <v>675</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731470</t>
+          <t xml:space="preserve">311733224</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-02</t>
+          <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørbækvej 47</t>
+          <t xml:space="preserve">St Byhavevej 67</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7606,15 +7606,15 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H127">
-        <v>810</v>
+        <v>351</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733214</t>
+          <t xml:space="preserve">311733224</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørbækvej 51</t>
+          <t xml:space="preserve">Ørbækvej 47</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7666,11 +7666,11 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H128">
-        <v>289</v>
+        <v>810</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørbækvej 53</t>
+          <t xml:space="preserve">Ørbækvej 47</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7726,11 +7726,11 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H129">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -7786,11 +7786,11 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H130">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -7846,11 +7846,11 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H131">
-        <v>269</v>
+        <v>1269</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">St Byhavevej 67</t>
+          <t xml:space="preserve">Ørbækvej 51</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7906,15 +7906,15 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H132">
-        <v>675</v>
+        <v>289</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733214</t>
+          <t xml:space="preserve">311733225</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">St Byhavevej 67</t>
+          <t xml:space="preserve">Ørbækvej 53</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7966,15 +7966,15 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H133">
-        <v>351</v>
+        <v>261</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733214</t>
+          <t xml:space="preserve">311733225</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørbækvej 47</t>
+          <t xml:space="preserve">Christiansvej 45A</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8021,25 +8021,25 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5496106</t>
+          <t xml:space="preserve">100110802</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H134">
-        <v>1269</v>
+        <v>268</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733214</t>
+          <t xml:space="preserve">311733638</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-15</t>
+          <t xml:space="preserve">2034-01-17</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christiansvej 45A</t>
+          <t xml:space="preserve">Fruerstuevej 17A</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,20 +8081,20 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">100110802</t>
+          <t xml:space="preserve">5493557</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H135">
-        <v>268</v>
+        <v>373</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733638</t>
+          <t xml:space="preserve">311733627</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fruerstuevej 17A</t>
+          <t xml:space="preserve">Linkenkærsvej 30</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8141,20 +8141,20 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493557</t>
+          <t xml:space="preserve">5496837</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H136">
-        <v>373</v>
+        <v>550</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733627</t>
+          <t xml:space="preserve">311733632</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8191,35 +8191,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linkenkærsvej 30</t>
+          <t xml:space="preserve">Assensvej 16</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5771</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5496837</t>
+          <t xml:space="preserve">9530274</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H137">
-        <v>550</v>
+        <v>1047</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733632</t>
+          <t xml:space="preserve">311736864</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-17</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,30 +8251,30 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 12</t>
+          <t xml:space="preserve">Assensvej 18</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5771</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">100047171</t>
+          <t xml:space="preserve">9530274</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H138">
-        <v>656</v>
+        <v>369</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736881</t>
+          <t xml:space="preserve">311736860</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8311,30 +8311,30 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storkehavevej 5</t>
+          <t xml:space="preserve">Assensvej 18</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5884</t>
+          <t xml:space="preserve">5771</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3025373</t>
+          <t xml:space="preserve">9530274</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H139">
-        <v>333</v>
+        <v>2655</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736855</t>
+          <t xml:space="preserve">311736860</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8371,30 +8371,30 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammesbrovej 11</t>
+          <t xml:space="preserve">Assensvej 18</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5883</t>
+          <t xml:space="preserve">5771</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3027337</t>
+          <t xml:space="preserve">9530274</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H140">
-        <v>439</v>
+        <v>583</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736852</t>
+          <t xml:space="preserve">311736861</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8431,30 +8431,30 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 19</t>
+          <t xml:space="preserve">Frederiksø 2</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5771</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042676</t>
+          <t xml:space="preserve">5492636</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H141">
-        <v>295</v>
+        <v>1491</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736870</t>
+          <t xml:space="preserve">311736908</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8491,17 +8491,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Færgevej 13</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5771</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042704</t>
+          <t xml:space="preserve">9496868</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -8510,11 +8510,11 @@
         </is>
       </c>
       <c r="H142">
-        <v>3282</v>
+        <v>268</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736857</t>
+          <t xml:space="preserve">311736772</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8551,17 +8551,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4</t>
+          <t xml:space="preserve">Grubbemøllevej 20</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5771</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042704</t>
+          <t xml:space="preserve">304213</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8570,11 +8570,11 @@
         </is>
       </c>
       <c r="H143">
-        <v>344</v>
+        <v>555</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736857</t>
+          <t xml:space="preserve">311736874</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8611,30 +8611,30 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Hammesbrovej 11</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5771</t>
+          <t xml:space="preserve">5883</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3042704</t>
+          <t xml:space="preserve">3027337</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H144">
-        <v>1578</v>
+        <v>439</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736857</t>
+          <t xml:space="preserve">311736852</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllergade 99</t>
+          <t xml:space="preserve">Jernbanegade 12</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,20 +8741,20 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5491669</t>
+          <t xml:space="preserve">100047171</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H146">
-        <v>397</v>
+        <v>656</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736787</t>
+          <t xml:space="preserve">311736881</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksø 2</t>
+          <t xml:space="preserve">Møllergade 99</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8801,20 +8801,20 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5492636</t>
+          <t xml:space="preserve">5491669</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H147">
-        <v>1491</v>
+        <v>397</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736908</t>
+          <t xml:space="preserve">311736787</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8971,17 +8971,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 1</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5771</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">9353541</t>
+          <t xml:space="preserve">3042704</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8990,11 +8990,11 @@
         </is>
       </c>
       <c r="H150">
-        <v>1461</v>
+        <v>3282</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736866</t>
+          <t xml:space="preserve">311736857</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9031,30 +9031,30 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Færgevej 13</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5771</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496868</t>
+          <t xml:space="preserve">3042704</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H151">
-        <v>268</v>
+        <v>1578</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736772</t>
+          <t xml:space="preserve">311736857</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assensvej 18</t>
+          <t xml:space="preserve">Skolevej 4</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -9101,20 +9101,20 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530274</t>
+          <t xml:space="preserve">3042704</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H152">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736860</t>
+          <t xml:space="preserve">311736857</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assensvej 18</t>
+          <t xml:space="preserve">Stationsvej 19</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9161,20 +9161,20 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530274</t>
+          <t xml:space="preserve">3042676</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H153">
-        <v>2655</v>
+        <v>295</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736860</t>
+          <t xml:space="preserve">311736870</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9211,30 +9211,30 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assensvej 18</t>
+          <t xml:space="preserve">Storkehavevej 5</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5771</t>
+          <t xml:space="preserve">5884</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530274</t>
+          <t xml:space="preserve">3025373</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H154">
-        <v>583</v>
+        <v>333</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736861</t>
+          <t xml:space="preserve">311736855</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9271,30 +9271,30 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assensvej 16</t>
+          <t xml:space="preserve">Svinget 1</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5771</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9530274</t>
+          <t xml:space="preserve">9353541</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H155">
-        <v>1047</v>
+        <v>1461</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736864</t>
+          <t xml:space="preserve">311736865</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737156</t>
+          <t xml:space="preserve">311737158</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737156</t>
+          <t xml:space="preserve">311737158</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737156</t>
+          <t xml:space="preserve">311737158</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 63B</t>
+          <t xml:space="preserve">Engdraget 2</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3036009</t>
+          <t xml:space="preserve">7198165</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -9830,11 +9830,11 @@
         </is>
       </c>
       <c r="H164">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741805</t>
+          <t xml:space="preserve">311741807</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 2</t>
+          <t xml:space="preserve">Eskærvej 50</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">7198165</t>
+          <t xml:space="preserve">8179274</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9890,11 +9890,11 @@
         </is>
       </c>
       <c r="H165">
-        <v>550</v>
+        <v>667</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741807</t>
+          <t xml:space="preserve">311741806</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 50</t>
+          <t xml:space="preserve">Eskærvej 63B</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8179274</t>
+          <t xml:space="preserve">3036009</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,11 +9950,11 @@
         </is>
       </c>
       <c r="H166">
-        <v>667</v>
+        <v>566</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311741806</t>
+          <t xml:space="preserve">311741805</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryttervej 70</t>
+          <t xml:space="preserve">Johs Jørgensens Vej 10</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10121,20 +10121,20 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">732757, 7977454</t>
+          <t xml:space="preserve">9496873</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H169">
-        <v>5293</v>
+        <v>3856</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742672</t>
+          <t xml:space="preserve">311742680</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johs Jørgensens Vej 10</t>
+          <t xml:space="preserve">Ryttervej 70</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10181,20 +10181,20 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496873</t>
+          <t xml:space="preserve">732757, 7977454</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H170">
-        <v>3856</v>
+        <v>5293</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742680</t>
+          <t xml:space="preserve">311742672</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipsvænget 19G</t>
+          <t xml:space="preserve">Gyldenbjergsvej 31</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295421</t>
+          <t xml:space="preserve">8900464</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10250,11 +10250,11 @@
         </is>
       </c>
       <c r="H171">
-        <v>306</v>
+        <v>2078</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743323</t>
+          <t xml:space="preserve">311743372</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipsvænget 19K</t>
+          <t xml:space="preserve">Gyldenbjergsvej 31</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10301,20 +10301,20 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295421</t>
+          <t xml:space="preserve">8900464</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H172">
-        <v>1152</v>
+        <v>1301</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743324</t>
+          <t xml:space="preserve">311743377</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipsvænget 19A</t>
+          <t xml:space="preserve">Gyldenbjergsvej 31</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10361,20 +10361,20 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295421</t>
+          <t xml:space="preserve">8900464</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H173">
-        <v>557</v>
+        <v>2050</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743333</t>
+          <t xml:space="preserve">311743372</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tipsvænget 19F</t>
+          <t xml:space="preserve">Gyldenbjergsvej 31</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10421,20 +10421,20 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295421</t>
+          <t xml:space="preserve">8900464</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H174">
-        <v>1113</v>
+        <v>1361</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743325</t>
+          <t xml:space="preserve">311743372</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10486,11 +10486,11 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H175">
-        <v>2078</v>
+        <v>550</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldenbjergsvej 31</t>
+          <t xml:space="preserve">Sofielund 2</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10541,20 +10541,20 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8900464</t>
+          <t xml:space="preserve">9496913</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H176">
-        <v>1301</v>
+        <v>1181</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743377</t>
+          <t xml:space="preserve">311743174</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldenbjergsvej 31</t>
+          <t xml:space="preserve">Tipsvænget 19A</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10601,20 +10601,20 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8900464</t>
+          <t xml:space="preserve">8295421</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="H177">
-        <v>2050</v>
+        <v>557</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743372</t>
+          <t xml:space="preserve">311743333</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldenbjergsvej 31</t>
+          <t xml:space="preserve">Tipsvænget 19F</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10661,20 +10661,20 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8900464</t>
+          <t xml:space="preserve">8295421</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H178">
-        <v>1361</v>
+        <v>1113</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743372</t>
+          <t xml:space="preserve">311743325</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldenbjergsvej 31</t>
+          <t xml:space="preserve">Tipsvænget 19G</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10721,20 +10721,20 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">8900464</t>
+          <t xml:space="preserve">8295421</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H179">
-        <v>550</v>
+        <v>306</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743372</t>
+          <t xml:space="preserve">311743323</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sofielund 2</t>
+          <t xml:space="preserve">Tipsvænget 19K</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10781,20 +10781,20 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496913</t>
+          <t xml:space="preserve">8295421</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H180">
-        <v>1181</v>
+        <v>1152</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743174</t>
+          <t xml:space="preserve">311743324</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dyrekredsen 12</t>
+          <t xml:space="preserve">Centrumpladsen 3</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3036596</t>
+          <t xml:space="preserve">9496867</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11030,11 +11030,11 @@
         </is>
       </c>
       <c r="H184">
-        <v>2720</v>
+        <v>1754</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750522</t>
+          <t xml:space="preserve">311750518</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskærvej 65A</t>
+          <t xml:space="preserve">Dyrekredsen 12</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11081,20 +11081,20 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">732766, 3035967</t>
+          <t xml:space="preserve">3036596</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H185">
-        <v>2168</v>
+        <v>2720</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750512</t>
+          <t xml:space="preserve">311750522</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 4A</t>
+          <t xml:space="preserve">Eskærvej 65A</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">732767, 3046461</t>
+          <t xml:space="preserve">732766, 3035967</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -11150,11 +11150,11 @@
         </is>
       </c>
       <c r="H186">
-        <v>2292</v>
+        <v>2168</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750509</t>
+          <t xml:space="preserve">311750512</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centrumpladsen 3</t>
+          <t xml:space="preserve">Skolevej 4A</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11261,20 +11261,20 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">9496867</t>
+          <t xml:space="preserve">732767, 3046461</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H188">
-        <v>1754</v>
+        <v>2292</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750518</t>
+          <t xml:space="preserve">311750509</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 6</t>
+          <t xml:space="preserve">Abildvej 2</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11926,15 +11926,15 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H199">
-        <v>447</v>
+        <v>1602</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311828739</t>
+          <t xml:space="preserve">311828740</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 2</t>
+          <t xml:space="preserve">Abildvej 6</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11986,15 +11986,15 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H200">
-        <v>1602</v>
+        <v>447</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311828740</t>
+          <t xml:space="preserve">311828739</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12091,17 +12091,17 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eriksholmsvej 2</t>
+          <t xml:space="preserve">Byvej 11</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700</t>
+          <t xml:space="preserve">5892</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">100516258</t>
+          <t xml:space="preserve">3024601</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -12110,11 +12110,11 @@
         </is>
       </c>
       <c r="H202">
-        <v>1160</v>
+        <v>2393</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885461</t>
+          <t xml:space="preserve">311885460</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 11</t>
+          <t xml:space="preserve">Byvej 15</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12166,11 +12166,11 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H203">
-        <v>2393</v>
+        <v>441</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -12211,30 +12211,30 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvej 15</t>
+          <t xml:space="preserve">Eriksholmsvej 2</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5892</t>
+          <t xml:space="preserve">5700</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">3024601</t>
+          <t xml:space="preserve">100516258</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H204">
-        <v>441</v>
+        <v>1160</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885460</t>
+          <t xml:space="preserve">311885461</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">

--- a/public/exports/29189730.xlsx
+++ b/public/exports/29189730.xlsx
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654750</t>
+          <t xml:space="preserve">311654753</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689549</t>
+          <t xml:space="preserve">311689544</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710301</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710293</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725288</t>
+          <t xml:space="preserve">311725279</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725281</t>
+          <t xml:space="preserve">311725279</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725283</t>
+          <t xml:space="preserve">311725279</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725284</t>
+          <t xml:space="preserve">311725279</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733224</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733224</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733225</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733225</t>
+          <t xml:space="preserve">311733214</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736857</t>
+          <t xml:space="preserve">311736859</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736857</t>
+          <t xml:space="preserve">311736859</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736857</t>
+          <t xml:space="preserve">311736859</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737158</t>
+          <t xml:space="preserve">311737156</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737158</t>
+          <t xml:space="preserve">311737156</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737158</t>
+          <t xml:space="preserve">311737156</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743333</t>
+          <t xml:space="preserve">311743330</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743324</t>
+          <t xml:space="preserve">311743330</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">

--- a/public/exports/29189730.xlsx
+++ b/public/exports/29189730.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:M205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1319,15 +1424,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t xml:space="preserve">Arkitektfirmaet Arne Birk</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-07-09</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1379,15 +1489,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t xml:space="preserve">Arkitektfirmaet Arne Birk</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-07-10</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1439,15 +1554,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Arkitektfirmaet Arne Birk</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-13</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1499,15 +1619,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-19</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1559,15 +1684,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Aalborg)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-08-21</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1619,15 +1749,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK aps</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-05-15</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1679,15 +1814,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1739,15 +1879,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Højbjerg Energimærkning</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1799,15 +1944,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-09-26</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1859,15 +2009,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1919,15 +2074,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1974,20 +2134,25 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654753</t>
+          <t xml:space="preserve">311654750</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2039,15 +2204,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2099,15 +2269,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2159,15 +2334,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2219,15 +2399,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2279,15 +2464,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2339,15 +2529,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2394,20 +2589,25 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654758</t>
+          <t xml:space="preserve">311654760</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-01-23</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-15</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-24</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-04-13</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-05-11</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3594,20 +3889,25 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689543</t>
+          <t xml:space="preserve">311689544</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3654,20 +3954,25 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689543</t>
+          <t xml:space="preserve">311689544</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3714,20 +4019,25 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689544</t>
+          <t xml:space="preserve">311689549</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-06-21</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3774,20 +4084,25 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698030</t>
+          <t xml:space="preserve">311698034</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3834,20 +4149,25 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698032</t>
+          <t xml:space="preserve">311698034</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-04</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-08-21</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-05</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-05</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-08</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4674,20 +5059,25 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706715</t>
+          <t xml:space="preserve">311706717</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-18</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-19</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-22</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-22</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-22</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-22</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6114,20 +6619,25 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710303</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-26</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-26</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6234,20 +6749,25 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710304</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-26</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6294,20 +6814,25 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710306</t>
+          <t xml:space="preserve">311710302</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-26</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-26</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-09-26</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-10-30</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6534,20 +7074,25 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725279</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6594,20 +7139,25 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725279</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6654,20 +7204,25 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725279</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6714,20 +7269,25 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725279</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6774,20 +7334,25 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725277</t>
+          <t xml:space="preserve">311725276</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-28</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-05</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-12</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-02</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-02</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-02</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-15</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-17</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-17</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-01-17</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8994,20 +9739,25 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736859</t>
+          <t xml:space="preserve">311736857</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9054,20 +9804,25 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736859</t>
+          <t xml:space="preserve">311736857</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9114,20 +9869,25 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736859</t>
+          <t xml:space="preserve">311736857</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9294,20 +10064,25 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736865</t>
+          <t xml:space="preserve">311736866</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9354,20 +10129,25 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737156</t>
+          <t xml:space="preserve">311737158</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-05</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9414,20 +10194,25 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737156</t>
+          <t xml:space="preserve">311737158</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-05</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9474,20 +10259,25 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737156</t>
+          <t xml:space="preserve">311737158</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-05</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-09</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-20</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-22</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-28</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-04</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-04</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-04</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10614,20 +11494,25 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743330</t>
+          <t xml:space="preserve">311743333</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10794,20 +11689,25 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743330</t>
+          <t xml:space="preserve">311743324</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10854,20 +11754,25 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744546</t>
+          <t xml:space="preserve">311744548</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-12</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-13</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-19</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-09</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-09</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-09</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-09</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-09</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-16</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-14</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-10-28</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-26</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-16</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-16</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-01</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-01</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimanden ApS</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-06</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-04</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-04</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-04</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,21 +13319,26 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">CB Group ApS</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-04</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gyldigt</t>
-        </is>
-      </c>
       <c r="L205" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gyldigt</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L205"/>
+  <autoFilter ref="A1:M205"/>
 </worksheet>
 </file>
--- a/public/exports/29189730.xlsx
+++ b/public/exports/29189730.xlsx
@@ -2589,7 +2589,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654760</t>
+          <t xml:space="preserve">311654758</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689544</t>
+          <t xml:space="preserve">311689543</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689544</t>
+          <t xml:space="preserve">311689543</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311689549</t>
+          <t xml:space="preserve">311689544</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698034</t>
+          <t xml:space="preserve">311698030</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698034</t>
+          <t xml:space="preserve">311698032</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706717</t>
+          <t xml:space="preserve">311706715</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710301</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710302</t>
+          <t xml:space="preserve">311710293</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736866</t>
+          <t xml:space="preserve">311736865</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737158</t>
+          <t xml:space="preserve">311737156</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737158</t>
+          <t xml:space="preserve">311737156</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737158</t>
+          <t xml:space="preserve">311737156</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743333</t>
+          <t xml:space="preserve">311743330</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energimanden ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311744548</t>
+          <t xml:space="preserve">311744546</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
